--- a/input/timetable/Магистратура_История.xlsx
+++ b/input/timetable/Магистратура_История.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13305" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13830" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="24" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="63">
   <si>
     <t>пара</t>
   </si>
@@ -189,9 +189,6 @@
     <t>2025-2026</t>
   </si>
   <si>
-    <t>02.02.2026- 06.06.2026</t>
-  </si>
-  <si>
     <t>История постсоветской России (пр), ЭОиДОТ//</t>
   </si>
   <si>
@@ -205,13 +202,19 @@
   </si>
   <si>
     <t>День самостоятельной работы</t>
+  </si>
+  <si>
+    <t>02.02.2026-30.03.2026; 27.04.2026-22.06.2026</t>
+  </si>
+  <si>
+    <t>02.02.2026- 18.04.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +307,12 @@
       <name val="Open Sans"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Open Sans"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -867,31 +876,58 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -913,32 +949,32 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -960,33 +996,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1302,7 +1311,7 @@
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="2"/>
@@ -1407,8 +1416,10 @@
       <c r="A10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
+      <c r="C10" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="64"/>
       <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1432,34 +1443,34 @@
       <c r="B12" s="25">
         <v>6</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="67"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="76"/>
     </row>
     <row r="13" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="26"/>
       <c r="B13" s="27">
         <v>7</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="61"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="63"/>
     </row>
     <row r="14" spans="1:13" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="28"/>
       <c r="B14" s="29">
         <v>8</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="64"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="73"/>
       <c r="M14" s="30"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1469,34 +1480,34 @@
       <c r="B15" s="25">
         <v>6</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="70"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="79"/>
     </row>
     <row r="16" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="26"/>
       <c r="B16" s="27">
         <v>7</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="73"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="54"/>
     </row>
     <row r="17" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="32"/>
       <c r="B17" s="29">
         <v>8</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="64"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="73"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="31" t="s">
@@ -1505,34 +1516,34 @@
       <c r="B18" s="25">
         <v>6</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="58"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="51"/>
     </row>
     <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="26"/>
       <c r="B19" s="27">
         <v>7</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="73"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
     </row>
     <row r="20" spans="1:6" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="32"/>
       <c r="B20" s="29">
         <v>8</v>
       </c>
-      <c r="C20" s="74" t="s">
+      <c r="C20" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="75"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="76"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="57"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="31" t="s">
@@ -1541,34 +1552,34 @@
       <c r="B21" s="25">
         <v>6</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="79"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="60"/>
     </row>
     <row r="22" spans="1:6" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="26"/>
       <c r="B22" s="27">
         <v>7</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="63"/>
     </row>
     <row r="23" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="32"/>
       <c r="B23" s="29">
         <v>8</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="64"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="73"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="31" t="s">
@@ -1577,34 +1588,34 @@
       <c r="B24" s="25">
         <v>6</v>
       </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="58"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="33"/>
       <c r="B25" s="27">
         <v>7</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="61"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="63"/>
     </row>
     <row r="26" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="34"/>
       <c r="B26" s="29">
         <v>8</v>
       </c>
-      <c r="C26" s="62" t="s">
+      <c r="C26" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="73"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="35" t="s">
@@ -1613,54 +1624,54 @@
       <c r="B27" s="25">
         <v>1</v>
       </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="58"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="51"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="36"/>
       <c r="B28" s="27">
         <v>2</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="61"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63"/>
     </row>
     <row r="29" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="37"/>
       <c r="B29" s="38">
         <v>3</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="61"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63"/>
     </row>
     <row r="30" spans="1:6" ht="10.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="45"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="52"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="67"/>
     </row>
     <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="43"/>
       <c r="B31" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="55"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="70"/>
     </row>
     <row r="32" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="33" spans="2:5" x14ac:dyDescent="0.4">
@@ -1681,11 +1692,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
@@ -1702,6 +1708,11 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <conditionalFormatting sqref="C9:E9 C10 E10">
     <cfRule type="expression" priority="1">
@@ -1835,7 +1846,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
@@ -1861,34 +1872,34 @@
       <c r="B12" s="25">
         <v>6</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="67"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="76"/>
     </row>
     <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="26"/>
       <c r="B13" s="27">
         <v>7</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="85"/>
     </row>
     <row r="14" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="28"/>
       <c r="B14" s="29">
         <v>8</v>
       </c>
-      <c r="C14" s="89" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="91"/>
+      <c r="C14" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="82"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="31" t="s">
@@ -1897,34 +1908,34 @@
       <c r="B15" s="25">
         <v>6</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="70"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="79"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="26"/>
       <c r="B16" s="27">
         <v>7</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="94"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="85"/>
     </row>
     <row r="17" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="32"/>
       <c r="B17" s="29">
         <v>8</v>
       </c>
-      <c r="C17" s="89" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="91"/>
+      <c r="C17" s="80" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="82"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="31" t="s">
@@ -1933,34 +1944,34 @@
       <c r="B18" s="25">
         <v>6</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="58"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="51"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="26"/>
       <c r="B19" s="27">
         <v>7</v>
       </c>
-      <c r="C19" s="92" t="s">
+      <c r="C19" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="94"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="85"/>
     </row>
     <row r="20" spans="1:6" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="32"/>
       <c r="B20" s="29">
         <v>8</v>
       </c>
-      <c r="C20" s="95" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="97"/>
+      <c r="C20" s="86" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="88"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="31" t="s">
@@ -1969,34 +1980,34 @@
       <c r="B21" s="25">
         <v>6</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="79"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="60"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="26"/>
       <c r="B22" s="27">
         <v>7</v>
       </c>
-      <c r="C22" s="92" t="s">
+      <c r="C22" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="94"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="85"/>
     </row>
     <row r="23" spans="1:6" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="32"/>
       <c r="B23" s="29">
         <v>8</v>
       </c>
-      <c r="C23" s="89" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="91"/>
+      <c r="C23" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="82"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="31" t="s">
@@ -2005,32 +2016,32 @@
       <c r="B24" s="25">
         <v>6</v>
       </c>
-      <c r="C24" s="83" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="85"/>
+      <c r="C24" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94"/>
     </row>
     <row r="25" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="33"/>
       <c r="B25" s="27">
         <v>7</v>
       </c>
-      <c r="C25" s="86"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="88"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="97"/>
     </row>
     <row r="26" spans="1:6" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="34"/>
       <c r="B26" s="29">
         <v>8</v>
       </c>
-      <c r="C26" s="80"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81"/>
-      <c r="F26" s="82"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="91"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="47" t="s">
@@ -2039,32 +2050,32 @@
       <c r="B27" s="39">
         <v>2</v>
       </c>
-      <c r="C27" s="83" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="85"/>
+      <c r="C27" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="94"/>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="36"/>
       <c r="B28" s="27">
         <v>3</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="88"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="97"/>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="48"/>
       <c r="B29" s="29">
         <v>4</v>
       </c>
-      <c r="C29" s="80"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="82"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="91"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B31" s="2" t="s">
@@ -2084,6 +2095,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
@@ -2096,12 +2113,6 @@
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7"/>

--- a/input/timetable/Магистратура_История.xlsx
+++ b/input/timetable/Магистратура_История.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13830" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13830"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="24" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="75">
   <si>
     <t>пара</t>
   </si>
@@ -69,6 +69,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -108,6 +111,15 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Прищепа А.И.</t>
+  </si>
+  <si>
+    <t>Веселов С.И.</t>
+  </si>
+  <si>
+    <t>Лешукова Е.В.</t>
+  </si>
+  <si>
     <t>История постсоветской России (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -117,6 +129,9 @@
     <t>Практикум по межкультурной коммуникации, ЭОиДОТ</t>
   </si>
   <si>
+    <t>Калантарян Г.А.</t>
+  </si>
+  <si>
     <t>Основы научных исследований в области исторических наук (лек 16 ч), ЭОиДОТ</t>
   </si>
   <si>
@@ -162,9 +177,18 @@
     <t>Историческая политика и историческая память в России (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Гололобов Е.И.</t>
+  </si>
+  <si>
+    <t>Задорожняя О.А.</t>
+  </si>
+  <si>
     <t>Организация генеалогических исследований (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Артеменко Р.В.</t>
+  </si>
+  <si>
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
@@ -189,7 +213,19 @@
     <t>2025-2026</t>
   </si>
   <si>
+    <t>Кулагина И.В</t>
+  </si>
+  <si>
+    <t>Кирилюк Д.В./Артеменко Р.В.</t>
+  </si>
+  <si>
+    <t>Кулагина И.В/.Артеменко Р.В.</t>
+  </si>
+  <si>
     <t>История постсоветской России (пр), ЭОиДОТ//</t>
+  </si>
+  <si>
+    <t>Сердюков Д.В.</t>
   </si>
   <si>
     <t>Историческая политика и историческая память в России (пр), ЭОиДОТ//</t>
@@ -314,7 +350,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,12 +369,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -418,6 +460,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -511,6 +611,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -651,6 +764,21 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -756,7 +884,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -799,28 +927,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -841,6 +972,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -850,13 +982,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
@@ -866,137 +998,145 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -1305,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1314,10 +1454,11 @@
     <col min="4" max="4" width="17.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1325,29 +1466,29 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1357,27 +1498,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="40" t="s">
-        <v>17</v>
+      <c r="C7" s="42" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -1387,44 +1528,44 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="41"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="15" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="42"/>
+        <v>27</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="44"/>
       <c r="E9" s="17"/>
     </row>
-    <row r="10" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="64"/>
+        <v>29</v>
+      </c>
+      <c r="C10" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="107"/>
       <c r="E10" s="17"/>
     </row>
-    <row r="11" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>0</v>
@@ -1435,245 +1576,294 @@
       <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="23"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A12" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="25">
+      <c r="G11" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="26">
         <v>6</v>
       </c>
       <c r="C12" s="74"/>
       <c r="D12" s="75"/>
       <c r="E12" s="75"/>
       <c r="F12" s="76"/>
-    </row>
-    <row r="13" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="G12" s="33"/>
+    </row>
+    <row r="13" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>7</v>
       </c>
-      <c r="C13" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="63"/>
-    </row>
-    <row r="14" spans="1:13" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
+      <c r="C13" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>8</v>
       </c>
       <c r="C14" s="71" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D14" s="72"/>
       <c r="E14" s="72"/>
       <c r="F14" s="73"/>
-      <c r="M14" s="30"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="25">
+      <c r="G14" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="31"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="26">
         <v>6</v>
       </c>
       <c r="C15" s="77"/>
       <c r="D15" s="78"/>
       <c r="E15" s="78"/>
       <c r="F15" s="79"/>
-    </row>
-    <row r="16" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="G15" s="33"/>
+    </row>
+    <row r="16" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>7</v>
       </c>
-      <c r="C16" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="54"/>
-    </row>
-    <row r="17" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="29">
+      <c r="C16" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="34"/>
+      <c r="B17" s="30">
         <v>8</v>
       </c>
       <c r="C17" s="71" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D17" s="72"/>
       <c r="E17" s="72"/>
       <c r="F17" s="73"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="G17" s="55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="26">
         <v>6</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="51"/>
-    </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="33"/>
+    </row>
+    <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>7</v>
       </c>
-      <c r="C19" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="54"/>
-    </row>
-    <row r="20" spans="1:6" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="32"/>
-      <c r="B20" s="29">
+      <c r="C19" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="34"/>
+      <c r="B20" s="30">
         <v>8</v>
       </c>
-      <c r="C20" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="57"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="25">
+      <c r="C20" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="26">
         <v>6</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="60"/>
-    </row>
-    <row r="22" spans="1:6" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="C21" s="86"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="33"/>
+    </row>
+    <row r="22" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28">
         <v>7</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="34"/>
+      <c r="B23" s="30">
+        <v>8</v>
+      </c>
+      <c r="C23" s="71" t="s">
         <v>44</v>
-      </c>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
-    </row>
-    <row r="23" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="32"/>
-      <c r="B23" s="29">
-        <v>8</v>
-      </c>
-      <c r="C23" s="71" t="s">
-        <v>39</v>
       </c>
       <c r="D23" s="72"/>
       <c r="E23" s="72"/>
       <c r="F23" s="73"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="25">
+      <c r="G23" s="55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="26">
         <v>6</v>
       </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="51"/>
-    </row>
-    <row r="25" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="33"/>
-      <c r="B25" s="27">
+      <c r="C24" s="65"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="33"/>
+    </row>
+    <row r="25" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="35"/>
+      <c r="B25" s="28">
         <v>7</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="36"/>
+      <c r="B26" s="30">
+        <v>8</v>
+      </c>
+      <c r="C26" s="71" t="s">
         <v>41</v>
-      </c>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63"/>
-    </row>
-    <row r="26" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="34"/>
-      <c r="B26" s="29">
-        <v>8</v>
-      </c>
-      <c r="C26" s="71" t="s">
-        <v>36</v>
       </c>
       <c r="D26" s="72"/>
       <c r="E26" s="72"/>
       <c r="F26" s="73"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="25">
+      <c r="G26" s="55" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="26">
         <v>1</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="51"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="36"/>
-      <c r="B28" s="27">
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="52"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="38"/>
+      <c r="B28" s="28">
         <v>2</v>
       </c>
-      <c r="C28" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63"/>
-    </row>
-    <row r="29" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38">
+      <c r="C28" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="39"/>
+      <c r="B29" s="40">
         <v>3</v>
       </c>
-      <c r="C29" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63"/>
-    </row>
-    <row r="30" spans="1:6" ht="10.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="45"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="67"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="68" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="70"/>
-    </row>
-    <row r="32" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="C29" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="10.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="47"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="49"/>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="45"/>
+      <c r="B31" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="33" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
         <v>14</v>
@@ -1692,6 +1882,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
@@ -1708,11 +1903,6 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <conditionalFormatting sqref="C9:E9 C10 E10">
     <cfRule type="expression" priority="1">
@@ -1735,7 +1925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1743,10 +1933,11 @@
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="5" width="18.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1754,29 +1945,29 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1786,27 +1977,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="40" t="s">
-        <v>17</v>
+      <c r="C7" s="42" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -1816,44 +2007,44 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>19</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>62</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>74</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
     </row>
-    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>0</v>
@@ -1864,220 +2055,257 @@
       <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="23"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="25">
+      <c r="G11" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="26">
         <v>6</v>
       </c>
       <c r="C12" s="74"/>
       <c r="D12" s="75"/>
       <c r="E12" s="75"/>
       <c r="F12" s="76"/>
-    </row>
-    <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="G12" s="33"/>
+    </row>
+    <row r="13" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>7</v>
       </c>
-      <c r="C13" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="85"/>
-    </row>
-    <row r="14" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
+      <c r="C13" s="101" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>8</v>
       </c>
-      <c r="C14" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="82"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="25">
+      <c r="C14" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="55" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="26">
         <v>6</v>
       </c>
       <c r="C15" s="77"/>
       <c r="D15" s="78"/>
       <c r="E15" s="78"/>
       <c r="F15" s="79"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="G15" s="33"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>7</v>
       </c>
-      <c r="C16" s="83" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="85"/>
-    </row>
-    <row r="17" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="29">
+      <c r="C16" s="101" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="54" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="34"/>
+      <c r="B17" s="30">
         <v>8</v>
       </c>
-      <c r="C17" s="80" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="82"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="C17" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="55" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="26">
         <v>6</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="51"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="33"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>7</v>
       </c>
-      <c r="C19" s="83" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="85"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="32"/>
-      <c r="B20" s="29">
+      <c r="C19" s="101" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="34"/>
+      <c r="B20" s="30">
         <v>8</v>
       </c>
-      <c r="C20" s="86" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="88"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="25">
+      <c r="C20" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="26">
         <v>6</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="60"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="C21" s="86"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="33"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28">
         <v>7</v>
       </c>
-      <c r="C22" s="83" t="s">
+      <c r="C22" s="101" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="85"/>
-    </row>
-    <row r="23" spans="1:6" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="32"/>
-      <c r="B23" s="29">
+    </row>
+    <row r="23" spans="1:7" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="34"/>
+      <c r="B23" s="30">
         <v>8</v>
       </c>
-      <c r="C23" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="82"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="25">
+      <c r="C23" s="98" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="55" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="26">
         <v>6</v>
       </c>
       <c r="C24" s="92" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D24" s="93"/>
       <c r="E24" s="93"/>
       <c r="F24" s="94"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="33"/>
-      <c r="B25" s="27">
+      <c r="G24" s="33"/>
+    </row>
+    <row r="25" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="35"/>
+      <c r="B25" s="28">
         <v>7</v>
       </c>
       <c r="C25" s="95"/>
       <c r="D25" s="96"/>
       <c r="E25" s="96"/>
       <c r="F25" s="97"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="34"/>
-      <c r="B26" s="29">
+      <c r="G25" s="50"/>
+    </row>
+    <row r="26" spans="1:7" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="36"/>
+      <c r="B26" s="30">
         <v>8</v>
       </c>
       <c r="C26" s="89"/>
       <c r="D26" s="90"/>
       <c r="E26" s="90"/>
       <c r="F26" s="91"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="39">
+      <c r="G26" s="51"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="41">
         <v>2</v>
       </c>
       <c r="C27" s="92" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D27" s="93"/>
       <c r="E27" s="93"/>
       <c r="F27" s="94"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="36"/>
-      <c r="B28" s="27">
+      <c r="G27" s="57"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="38"/>
+      <c r="B28" s="28">
         <v>3</v>
       </c>
       <c r="C28" s="95"/>
       <c r="D28" s="96"/>
       <c r="E28" s="96"/>
       <c r="F28" s="97"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="48"/>
-      <c r="B29" s="29">
+      <c r="G28" s="54"/>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="58"/>
+      <c r="B29" s="30">
         <v>4</v>
       </c>
       <c r="C29" s="89"/>
       <c r="D29" s="90"/>
       <c r="E29" s="90"/>
       <c r="F29" s="91"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G29" s="51"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B31" s="2" t="s">
         <v>14</v>
       </c>
@@ -2085,7 +2313,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
@@ -2095,12 +2323,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
@@ -2113,6 +2335,12 @@
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7"/>
